--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104687_W26.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104687_W26.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.0846</v>
+        <v>9.6007</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4598</v>
+        <v>7.4335</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6249</v>
+        <v>2.1671</v>
       </c>
       <c r="G2" t="n">
-        <v>10.0076</v>
+        <v>9.968999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>4.6207</v>
+        <v>4.5966</v>
       </c>
       <c r="I2" t="n">
-        <v>5.3869</v>
+        <v>5.3724</v>
       </c>
       <c r="J2" t="n">
-        <v>10.9256</v>
+        <v>10.8579</v>
       </c>
       <c r="K2" t="n">
-        <v>5.52</v>
+        <v>5.4738</v>
       </c>
       <c r="L2" t="n">
-        <v>5.4055</v>
+        <v>5.384</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9179</v>
+        <v>-0.8888</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8993</v>
+        <v>-0.8772</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R2" t="n">
-        <v>3.6293</v>
+        <v>3.6421</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7227</v>
+        <v>-0.1604</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1825</v>
+        <v>-0.1189</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5402</v>
+        <v>-0.0414</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2237</v>
+        <v>4.5171</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7676</v>
+        <v>4.0473</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4562</v>
+        <v>0.4697</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7156</v>
+        <v>2.7169</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2438</v>
+        <v>2.2431</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1819</v>
+        <v>2.1718</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1819</v>
+        <v>2.1718</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5337</v>
+        <v>0.5451</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0619</v>
+        <v>0.0713</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7349</v>
+        <v>0.0278</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9467</v>
+        <v>0.2413</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2117</v>
+        <v>-0.2135</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. CACOK</t>
+          <t>W. FALK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5473</v>
+        <v>3.1752</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3786</v>
+        <v>2.2288</v>
       </c>
       <c r="F4" t="n">
-        <v>4.1687</v>
+        <v>0.9464</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3826</v>
+        <v>-0.1963</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8948</v>
+        <v>0.3816</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4878</v>
+        <v>-0.5778</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3306</v>
+        <v>-0.2839</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5097</v>
+        <v>0.2823</v>
       </c>
       <c r="L4" t="n">
-        <v>0.821</v>
+        <v>-0.5662</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.948</v>
+        <v>0.0876</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6149</v>
+        <v>0.0993</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3331</v>
+        <v>-0.0116</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5878</v>
+        <v>2.7316</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.5367</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3384</v>
+        <v>0.6399</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9417</v>
+        <v>0.4036</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3967</v>
+        <v>0.2363</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4141</v>
+        <v>-0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6429</v>
+        <v>2.3367</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7712</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W. FALK</t>
+          <t>D. CACOK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7657</v>
+        <v>2.7889</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9612</v>
+        <v>-0.8472</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8045</v>
+        <v>3.6362</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2075</v>
+        <v>1.3769</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3736</v>
+        <v>0.8851</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5810999999999999</v>
+        <v>0.4917</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.265</v>
+        <v>2.3081</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2975</v>
+        <v>1.4889</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5625</v>
+        <v>0.8192</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0575</v>
+        <v>-0.9312</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0761</v>
+        <v>-0.6037</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0186</v>
+        <v>-0.3275</v>
       </c>
       <c r="P5" t="n">
-        <v>2.722</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>-4.5526</v>
       </c>
       <c r="R5" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2512</v>
+        <v>1.6005</v>
       </c>
       <c r="T5" t="n">
-        <v>1.107</v>
+        <v>0.7662</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1442</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.405</v>
       </c>
       <c r="W5" t="n">
-        <v>2.3461</v>
+        <v>0.6311</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.3461</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. DIAGNE</t>
+          <t>J. RADEBAUGH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2881</v>
+        <v>1.7216</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1716</v>
+        <v>-2.403</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8835</v>
+        <v>4.1246</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8625</v>
+        <v>-2.4424</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5555</v>
+        <v>-1.2098</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-1.2325</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6056</v>
+        <v>-2.3721</v>
       </c>
       <c r="K6" t="n">
-        <v>2.4936</v>
+        <v>-0.9932</v>
       </c>
       <c r="L6" t="n">
-        <v>0.112</v>
+        <v>-1.3789</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7431</v>
+        <v>-0.0703</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0619</v>
+        <v>-0.2166</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.805</v>
+        <v>0.1463</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>3.6421</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>3.6421</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2914</v>
+        <v>0.2927</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0858</v>
+        <v>-0.1886</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2056</v>
+        <v>0.4813</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0927</v>
+        <v>0.2292</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7071</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7997</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9073</v>
+        <v>1.3374</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1102</v>
+        <v>2.3223</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.203</v>
+        <v>-0.9849</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5734</v>
+        <v>2.5777</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2193</v>
+        <v>1.2206</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3541</v>
+        <v>1.3572</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9351</v>
+        <v>2.9193</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0319</v>
+        <v>1.0202</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9032</v>
+        <v>1.8991</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3617</v>
+        <v>-0.3416</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1874</v>
+        <v>0.2003</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8003</v>
+        <v>-0.3785</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5565</v>
+        <v>-0.3207</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2438</v>
+        <v>-0.0578</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. RADEBAUGH</t>
+          <t>M. DIAGNE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7065</v>
+        <v>1.0369</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.4323</v>
+        <v>3.2125</v>
       </c>
       <c r="F8" t="n">
-        <v>4.1387</v>
+        <v>-2.1756</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.4406</v>
+        <v>1.8639</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2224</v>
+        <v>2.5534</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2183</v>
+        <v>-0.6895</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.3409</v>
+        <v>2.5938</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9839</v>
+        <v>2.4821</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3569</v>
+        <v>0.1117</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0998</v>
+        <v>-0.73</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2384</v>
+        <v>0.0713</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1387</v>
+        <v>-0.8012</v>
       </c>
       <c r="P8" t="n">
-        <v>3.6293</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>3.6293</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7071</v>
+        <v>0.0349</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2521</v>
+        <v>0.1438</v>
       </c>
       <c r="U8" t="n">
-        <v>0.545</v>
+        <v>-0.1089</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2249</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1607</v>
+        <v>0.7025</v>
       </c>
       <c r="X8" t="n">
-        <v>0.06419999999999999</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8742</v>
+        <v>-0.3031</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5599</v>
+        <v>-0.9863</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6857</v>
+        <v>0.6833</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4858</v>
+        <v>0.494</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2152</v>
+        <v>-0.2045</v>
       </c>
       <c r="I9" t="n">
-        <v>0.701</v>
+        <v>0.6985</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0743</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3708</v>
+        <v>-0.376</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4115</v>
+        <v>0.4308</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1556</v>
+        <v>0.1715</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5622</v>
+        <v>-0.0035</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0484</v>
+        <v>0.5454</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5139</v>
+        <v>-0.549</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0416</v>
+        <v>-0.8589</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8016</v>
+        <v>-0.6872</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.24</v>
+        <v>-0.1717</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2406</v>
+        <v>-1.2398</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.062</v>
+        <v>-1.0626</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1786</v>
+        <v>-0.1772</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6625</v>
+        <v>-0.6662</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6998</v>
+        <v>-0.7035</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5780999999999999</v>
+        <v>-0.5736</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3622</v>
+        <v>-0.3592</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0278</v>
+        <v>0.1533</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1391</v>
+        <v>-0.021</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1113</v>
+        <v>0.1743</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.452</v>
+        <v>-1.2699</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1368</v>
+        <v>0.2333</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5888</v>
+        <v>-1.5032</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9424</v>
+        <v>-0.9469</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2251</v>
+        <v>0.2241</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1675</v>
+        <v>-1.171</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6933</v>
+        <v>0.6725</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9973</v>
+        <v>0.9858</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3039</v>
+        <v>-0.3132</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6357</v>
+        <v>-1.6194</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3242</v>
+        <v>-0.144</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5565</v>
+        <v>-0.4392</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2323</v>
+        <v>0.2951</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1992</v>
+        <v>-2.0113</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2668</v>
+        <v>-0.1581</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9324</v>
+        <v>-1.8532</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0124</v>
+        <v>1.0129</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9351</v>
+        <v>0.9308</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1456</v>
+        <v>1.1404</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1083</v>
+        <v>1.1032</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1331</v>
+        <v>-0.1275</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="O12" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6388</v>
+        <v>-0.4599</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2782</v>
+        <v>-0.1604</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3605</v>
+        <v>-0.2995</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.079</v>
+        <v>-4.8673</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.5729</v>
+        <v>-3.3778</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5061</v>
+        <v>-1.4894</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.112</v>
+        <v>-0.1264</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5757</v>
+        <v>-0.5772</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4637</v>
+        <v>0.4508</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4738</v>
+        <v>0.4456</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.6485</v>
       </c>
       <c r="L13" t="n">
-        <v>1.1114</v>
+        <v>1.0941</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5858</v>
+        <v>-0.572</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0619</v>
+        <v>0.0713</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.1757</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6986</v>
+        <v>-0.4645</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4174</v>
+        <v>-0.1813</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2813</v>
+        <v>-0.2832</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.8772</v>
+        <v>14.8673</v>
       </c>
       <c r="E14" t="n">
-        <v>11.3523</v>
+        <v>11.0181</v>
       </c>
       <c r="F14" t="n">
-        <v>3.524900000000001</v>
+        <v>3.8493</v>
       </c>
       <c r="G14" t="n">
-        <v>15.0968</v>
+        <v>15.0595</v>
       </c>
       <c r="H14" t="n">
-        <v>9.992599999999999</v>
+        <v>9.981199999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>5.104100000000001</v>
+        <v>5.078499999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>20.0974</v>
+        <v>19.8504</v>
       </c>
       <c r="K14" t="n">
-        <v>12.4481</v>
+        <v>12.2869</v>
       </c>
       <c r="L14" t="n">
-        <v>7.649500000000001</v>
+        <v>7.563400000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.0005</v>
+        <v>-4.790900000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.4553</v>
+        <v>-2.3058</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.5451</v>
+        <v>-2.485</v>
       </c>
       <c r="P14" t="n">
-        <v>3.4024</v>
+        <v>3.414499999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-17.0125</v>
+        <v>-17.0723</v>
       </c>
       <c r="R14" t="n">
-        <v>20.4148</v>
+        <v>20.4868</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1342</v>
+        <v>1.138300000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6505000000000001</v>
+        <v>0.6702000000000002</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4837000000000001</v>
+        <v>0.4679</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.7564</v>
+        <v>-4.7449</v>
       </c>
       <c r="W14" t="n">
-        <v>7.617</v>
+        <v>7.5698</v>
       </c>
       <c r="X14" t="n">
-        <v>-12.3732</v>
+        <v>-12.3146</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1522</v>
+        <v>2.778</v>
       </c>
       <c r="E15" t="n">
-        <v>4.985</v>
+        <v>4.6809</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.8328</v>
+        <v>-1.9028</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.892</v>
+        <v>-0.8861</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4993</v>
+        <v>0.4943</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3913</v>
+        <v>-1.3804</v>
       </c>
       <c r="J15" t="n">
-        <v>2.014</v>
+        <v>1.9788</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0913</v>
+        <v>2.0609</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.906</v>
+        <v>-2.8649</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.592</v>
+        <v>-1.5667</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.314</v>
+        <v>-1.2982</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S15" t="n">
-        <v>0.352</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2692</v>
+        <v>0.0366</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0828</v>
+        <v>-0.0458</v>
       </c>
       <c r="V15" t="n">
-        <v>4.1458</v>
+        <v>4.1287</v>
       </c>
       <c r="W15" t="n">
-        <v>6.3311</v>
+        <v>6.3076</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1413</v>
+        <v>-0.1862</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8694</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0107</v>
+        <v>-0.9296</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9611</v>
+        <v>0.9683</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.7924</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1733</v>
+        <v>0.1759</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4773</v>
+        <v>1.4707</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4027</v>
+        <v>1.3962</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5162</v>
+        <v>-0.5023</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O16" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S16" t="n">
-        <v>0.444</v>
+        <v>0.3902</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5263</v>
+        <v>0.4109</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0823</v>
+        <v>-0.0207</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. JOHNSON</t>
+          <t>A. ALIBEGOVIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5014</v>
+        <v>-0.6385</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7935</v>
+        <v>-0.3117</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2949</v>
+        <v>-0.3267</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4172</v>
+        <v>-1.8849</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3132</v>
+        <v>-0.574</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1039</v>
+        <v>-1.311</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2159</v>
+        <v>1.2566</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1039</v>
+        <v>2.285</v>
       </c>
       <c r="L17" t="n">
-        <v>0.112</v>
+        <v>-1.0284</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.633</v>
+        <v>-3.1415</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4171</v>
+        <v>-2.859</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2159</v>
+        <v>-0.2826</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4537</v>
+        <v>2.5039</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4621</v>
+        <v>-0.5228</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5777</v>
+        <v>-0.6044</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1155</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.6311</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.4018</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ALIBEGOVIC</t>
+          <t>J. JOHNSON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.8985</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2471</v>
+        <v>0.3219</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6849</v>
+        <v>-1.2204</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8743</v>
+        <v>-1.4071</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5655</v>
+        <v>-1.3044</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3088</v>
+        <v>-0.1027</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3008</v>
+        <v>0.2151</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3164</v>
+        <v>0.1034</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.0157</v>
+        <v>0.1117</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.1751</v>
+        <v>-1.6223</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.8819</v>
+        <v>-1.4078</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2931</v>
+        <v>-0.2144</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4952</v>
+        <v>0.4553</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8347</v>
+        <v>0.0534</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6049</v>
+        <v>0.1067</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2299</v>
+        <v>-0.0534</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6429</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.418</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.2249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PEREZ</t>
+          <t>E. VALTONEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9587</v>
+        <v>-1.4003</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4015</v>
+        <v>-1.8321</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3602</v>
+        <v>0.4318</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5272</v>
+        <v>-0.6478</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4041</v>
+        <v>-1.9305</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8769</v>
+        <v>1.2827</v>
       </c>
       <c r="J19" t="n">
-        <v>2.182</v>
+        <v>1.5725</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0488</v>
+        <v>-0.5795</v>
       </c>
       <c r="L19" t="n">
-        <v>2.2309</v>
+        <v>2.1521</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7092</v>
+        <v>-2.2203</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3552</v>
+        <v>-1.351</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.354</v>
+        <v>-0.8694</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.361</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2683</v>
+        <v>2.9592</v>
       </c>
       <c r="S19" t="n">
-        <v>1.6365</v>
+        <v>-0.6143</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7561</v>
+        <v>-0.465</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8804</v>
+        <v>-0.1493</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7071</v>
+        <v>0.5447</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>0.7025</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7997</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. VALTONEN</t>
+          <t>J. PEREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1241</v>
+        <v>-1.4205</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7947</v>
+        <v>0.2391</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6706</v>
+        <v>-1.6595</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.66</v>
+        <v>-0.5309</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9395</v>
+        <v>-1.399</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2795</v>
+        <v>0.8681</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5933</v>
+        <v>2.1488</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5683</v>
+        <v>-0.0624</v>
       </c>
       <c r="L20" t="n">
-        <v>2.1617</v>
+        <v>2.2112</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.2533</v>
+        <v>-2.6797</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3711</v>
+        <v>-1.3365</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8822</v>
+        <v>-1.3432</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6805</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R20" t="n">
-        <v>2.9488</v>
+        <v>2.2763</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.33</v>
+        <v>1.1787</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4657</v>
+        <v>0.6429</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1358</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5463</v>
+        <v>-0.7025</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7071</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1607</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. ROUSSELLE</t>
+          <t>A. BRIMAH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9763</v>
+        <v>-1.9544</v>
       </c>
       <c r="E21" t="n">
-        <v>0.278</v>
+        <v>-0.5034</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2543</v>
+        <v>-1.451</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.318</v>
+        <v>-0.8453000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.267</v>
+        <v>0.7007</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9489</v>
+        <v>-1.546</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1873</v>
+        <v>0.5861</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3392</v>
+        <v>0.5861</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.152</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5053</v>
+        <v>-1.4314</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6062</v>
+        <v>0.1146</v>
       </c>
       <c r="O21" t="n">
-        <v>1.1009</v>
+        <v>-1.546</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q21" t="n">
+        <v>-1.1382</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.4553</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.4261</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.0487</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.4749</v>
+      </c>
+      <c r="V21" t="n">
         <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.4537</v>
-      </c>
-      <c r="S21" t="n">
-        <v>-0.1515</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.0907</v>
-      </c>
-      <c r="U21" t="n">
-        <v>-0.2423</v>
-      </c>
-      <c r="V21" t="n">
-        <v>-1.9604</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.9604</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. BRIMAH</t>
+          <t>J. ROUSSELLE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1695</v>
+        <v>-1.9709</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.615</v>
+        <v>-0.0886</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5545</v>
+        <v>-1.8823</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8529</v>
+        <v>-0.315</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6984</v>
+        <v>-1.2639</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5513</v>
+        <v>0.9489</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5888</v>
+        <v>0.1741</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5888</v>
+        <v>0.3308</v>
       </c>
       <c r="L22" t="n">
+        <v>-0.1566</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.4891</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-1.5946</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.1055</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.4553</v>
+      </c>
+      <c r="Q22" t="n">
         <v>0</v>
       </c>
-      <c r="M22" t="n">
-        <v>-1.4417</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.1096</v>
-      </c>
-      <c r="O22" t="n">
-        <v>-1.5513</v>
-      </c>
-      <c r="P22" t="n">
-        <v>-0.6805</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>-1.1342</v>
-      </c>
       <c r="R22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.636</v>
+        <v>-0.1615</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0696</v>
+        <v>-0.2627</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5665</v>
+        <v>0.1013</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.9497</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.9497</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2224</v>
+        <v>-2.1812</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4483</v>
+        <v>-0.1359</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7741</v>
+        <v>-2.0453</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8811</v>
+        <v>-2.8755</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3751</v>
+        <v>-1.3757</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.506</v>
+        <v>-1.4998</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5023</v>
+        <v>-0.5261</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3503</v>
+        <v>-0.3695</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.152</v>
+        <v>-0.1566</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.3788</v>
+        <v>-2.3494</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0248</v>
+        <v>-1.0062</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6835</v>
+        <v>-0.6456</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9557</v>
+        <v>-0.602</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2722</v>
+        <v>-0.0436</v>
       </c>
       <c r="V23" t="n">
-        <v>2.2495</v>
+        <v>2.2504</v>
       </c>
       <c r="W23" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0285</v>
+        <v>-1.018</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.0037</v>
+        <v>-6.9949</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.6547</v>
+        <v>-5.8734</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.349</v>
+        <v>-1.1216</v>
       </c>
       <c r="G24" t="n">
-        <v>-6.6353</v>
+        <v>-6.6352</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.1137</v>
+        <v>-4.121</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.5215</v>
+        <v>-2.5141</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.0565</v>
+        <v>-4.0858</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.4194</v>
+        <v>-3.4451</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6371</v>
+        <v>-0.6407</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.5788</v>
+        <v>-2.5494</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6944</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.8844</v>
+        <v>-1.8734</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R24" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3931</v>
+        <v>-0.3809</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6079</v>
+        <v>0.2203</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7852</v>
+        <v>-0.6012</v>
       </c>
       <c r="V24" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W24" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-14.8772</v>
+        <v>-14.8674</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.432399999999999</v>
+        <v>-2.759799999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-12.4448</v>
+        <v>-12.1074</v>
       </c>
       <c r="G25" t="n">
-        <v>-15.0969</v>
+        <v>-15.0595</v>
       </c>
       <c r="H25" t="n">
-        <v>-9.992599999999999</v>
+        <v>-9.981100000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-5.104200000000001</v>
+        <v>-5.0784</v>
       </c>
       <c r="J25" t="n">
-        <v>5.0006</v>
+        <v>4.7908</v>
       </c>
       <c r="K25" t="n">
-        <v>2.455499999999999</v>
+        <v>2.305900000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>2.5451</v>
+        <v>2.485099999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-20.0974</v>
+        <v>-19.8503</v>
       </c>
       <c r="N25" t="n">
-        <v>-12.448</v>
+        <v>-12.2868</v>
       </c>
       <c r="O25" t="n">
-        <v>-7.649400000000001</v>
+        <v>-7.563499999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.4024</v>
+        <v>-3.414399999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>-20.4149</v>
+        <v>-20.4869</v>
       </c>
       <c r="R25" t="n">
-        <v>17.0126</v>
+        <v>17.0724</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4837999999999999</v>
+        <v>-0.468</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6505</v>
+        <v>-0.6701999999999999</v>
       </c>
       <c r="V25" t="n">
-        <v>4.7563</v>
+        <v>4.7449</v>
       </c>
       <c r="W25" t="n">
-        <v>13.4659</v>
+        <v>13.404</v>
       </c>
       <c r="X25" t="n">
-        <v>-8.7095</v>
+        <v>-8.659199999999998</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104687_W26.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104687_W26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104687_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104687_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104687_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104687_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.07140000000000001</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104687_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104687_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104687_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104687_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104687_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104687_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104687_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104687_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-12.3146</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104687_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104687_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104687_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104687_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104687_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104687_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104687_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.9497</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104687_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.018</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104687_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104687_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-8.659199999999998</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
